--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1F3EA5-F442-48DD-B2EE-08EDFCB886DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -27,18 +35,63 @@
   </si>
   <si>
     <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>test@admin</t>
+  </si>
+  <si>
+    <t>$2a$12$CY4mlvyFac7J0xYP9Oo7A./NATiSIfPbT6mbB63S7d3S0Ls9eVAYC</t>
+  </si>
+  <si>
+    <t>01-01-2000</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Mihai14</t>
+  </si>
+  <si>
+    <t>mihai@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$mxUp6F8bN1WQ5U5oT0WKXOhFPNqQWCrj6xRXvSBndGUprNUZssx.y</t>
+  </si>
+  <si>
+    <t>15-05-2004</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Mihai12</t>
+  </si>
+  <si>
+    <t>mihaiviorelstan@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$WoJESHwqu30uw1c61qAWcOsQWTZskQ/4CzcJ6v390/ZS0Fe59490a</t>
+  </si>
+  <si>
+    <t>15-02-2000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -48,7 +101,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -66,22 +119,350 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="9.17578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="5.92578125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="8.61328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.1796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="66.76171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
@@ -98,7 +479,58 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serba\AppData\Roaming\SPB_Data\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1F3EA5-F442-48DD-B2EE-08EDFCB886DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF3B014-C8E1-4E5F-83CB-3E4AECC90F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -80,6 +80,45 @@
   </si>
   <si>
     <t>15-02-2000</t>
+  </si>
+  <si>
+    <t>$2a$12$kwjwLDgW5.yyK5l0bDbO3uUawRc.77RQZ1eZ32bmC1jIV1EIOhV9a</t>
+  </si>
+  <si>
+    <t>$2a$12$9YTuoKj6bZmyR7pHTZbAL.FZC7D/7xpxliPps4loZAAXLgUk5Q576</t>
+  </si>
+  <si>
+    <t>$2a$12$d4LQ0bY8aipPIDXmS0qnLOZuPWaLXLHnRdUhnu/N5pHnMzYoR3rwW</t>
+  </si>
+  <si>
+    <t>Serban123</t>
+  </si>
+  <si>
+    <t>s@y.com</t>
+  </si>
+  <si>
+    <t>$2a$12$WBL81iGG3XPCx9gH7hPJRe7edY2DPDJnBAviD6/n/IFPJ02UGgU3a</t>
+  </si>
+  <si>
+    <t>30-08-2000</t>
+  </si>
+  <si>
+    <t>$2a$12$mQxp63of/TPVUOx.IVzlWOhGBwl5ZcfpjEoLkzYS4CDebjHGHoP42</t>
+  </si>
+  <si>
+    <t>$2a$12$4Bw4NdHXJ.1ed2X/Jnz3X.n3CobsQt35EA6Mu0qVSNoWbD7sCRbeq</t>
+  </si>
+  <si>
+    <t>$2a$12$pcwaVErtO8XzrBU8aktfL.hA.xRE/Z9vVkoDAZf1l11R8rsCsiFny</t>
+  </si>
+  <si>
+    <t>$2a$12$FwGNUQoxjSsE9o9N0xxTOuChOhjb8GVkhFz7rqX3TgWqwU1rDVFtq</t>
+  </si>
+  <si>
+    <t>$2a$12$vgVwZl.BhCbITo8JEFu4zOuIgzO/XIcyglbh9QRjxomiTn8m0EX6e</t>
+  </si>
+  <si>
+    <t>$2a$12$0CdrxqVbob0qzfT3peq7buGqy4bU7o0.J4b3UHDHN.fc4Oou2hUle</t>
   </si>
 </sst>
 </file>
@@ -452,17 +491,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="66.76171875"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
@@ -479,7 +518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
         <v>5</v>
       </c>
@@ -496,7 +535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
@@ -513,7 +552,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
         <v>15</v>
       </c>
@@ -528,6 +567,176 @@
       </c>
       <c r="E4" t="s" s="0">
         <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1F3EA5-F442-48DD-B2EE-08EDFCB886DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DA16A1-D919-4849-A6DB-CC71D870E10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>ID</t>
   </si>
@@ -36,57 +36,11 @@
   <si>
     <t>Date of Birth</t>
   </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>test@admin</t>
-  </si>
-  <si>
-    <t>$2a$12$CY4mlvyFac7J0xYP9Oo7A./NATiSIfPbT6mbB63S7d3S0Ls9eVAYC</t>
-  </si>
-  <si>
-    <t>01-01-2000</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Mihai14</t>
-  </si>
-  <si>
-    <t>mihai@gmail.com</t>
-  </si>
-  <si>
-    <t>$2a$12$mxUp6F8bN1WQ5U5oT0WKXOhFPNqQWCrj6xRXvSBndGUprNUZssx.y</t>
-  </si>
-  <si>
-    <t>15-05-2004</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Mihai12</t>
-  </si>
-  <si>
-    <t>mihaiviorelstan@gmail.com</t>
-  </si>
-  <si>
-    <t>$2a$12$WoJESHwqu30uw1c61qAWcOsQWTZskQ/4CzcJ6v390/ZS0Fe59490a</t>
-  </si>
-  <si>
-    <t>15-02-2000</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -452,82 +406,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="66.76171875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -119,6 +119,36 @@
   </si>
   <si>
     <t>$2a$12$0CdrxqVbob0qzfT3peq7buGqy4bU7o0.J4b3UHDHN.fc4Oou2hUle</t>
+  </si>
+  <si>
+    <t>$2a$12$DKf0QJLMBsE1Hdsq7sTlWuqlqebw247P7lH9t1u.HaZZ6hv7uAHLq</t>
+  </si>
+  <si>
+    <t>$2a$12$iWKkKScGPqA8Ln6o4sezpOjUMhK47jflt66brWmljrkA.zogYfjCa</t>
+  </si>
+  <si>
+    <t>$2a$12$eXiy.07Cy.vq/f7xSvMvEupq99A7KNl3UxFt8tIyp5UdmWgiY2/KW</t>
+  </si>
+  <si>
+    <t>$2a$12$mEoXZJq.yRsJjs2XwuABleUVs8sF/ye6I6WLeh06PcqhZvUQLplL6</t>
+  </si>
+  <si>
+    <t>$2a$12$dTuY0JowgNNg6oFHk2xxH.ZJKBEsyVD/XTrUUH88drkYPussFgzeC</t>
+  </si>
+  <si>
+    <t>$2a$12$7crWFGlGwUf2qLXNVOLKBemQ0VWDnTi06MnXdXQrEyMkrVuPTPwCS</t>
+  </si>
+  <si>
+    <t>Serban12</t>
+  </si>
+  <si>
+    <t>s@y1.com</t>
+  </si>
+  <si>
+    <t>$2a$12$lL2Vd/OdYOnVOgcDtcy1Be.m5sHYA9jC.BAvwrQy9G.L0VuphvOJ6</t>
+  </si>
+  <si>
+    <t>30-07-2004</t>
   </si>
 </sst>
 </file>
@@ -491,13 +521,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="66.76171875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="67.06640625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
@@ -739,6 +769,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DA16A1-D919-4849-A6DB-CC71D870E10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798B4254-7D9D-4FBA-9192-C9BA1ECBDA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -35,12 +35,43 @@
   </si>
   <si>
     <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>test@admin</t>
+  </si>
+  <si>
+    <t>$2a$12$DDjfx2JAW.3U4n4HNJe/SO5WQTfFlLsmoN0bfb5I9aNKRDXBVVfzS</t>
+  </si>
+  <si>
+    <t>01-01-2000</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Mihai14</t>
+  </si>
+  <si>
+    <t>mihai@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$AomzYMZwq2MjzsPAN9kK3OM6OheRkKWP/FSsBfbCDMiWqxvixmn1.</t>
+  </si>
+  <si>
+    <t>11-09-1100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -406,31 +437,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.23046875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="65.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
@@ -149,6 +149,12 @@
   </si>
   <si>
     <t>30-07-2004</t>
+  </si>
+  <si>
+    <t>$2a$12$tV4kbUG0oLsMHPcZk3q/Zeg5u7dSvaFdEk71yG2TXt5N2H7GembQu</t>
+  </si>
+  <si>
+    <t>$2a$12$XCHM1x7/55PuiiHzCmPsYu/GKO9Q5LVZ2t3nZTZfa3dCVLum4uATa</t>
   </si>
 </sst>
 </file>
@@ -521,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
@@ -888,6 +894,40 @@
         <v>42</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798B4254-7D9D-4FBA-9192-C9BA1ECBDA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3AA2ED-248E-4D19-BB1F-F5DC9E904FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -46,7 +46,7 @@
     <t>test@admin</t>
   </si>
   <si>
-    <t>$2a$12$DDjfx2JAW.3U4n4HNJe/SO5WQTfFlLsmoN0bfb5I9aNKRDXBVVfzS</t>
+    <t>$2a$12$.8f5of5jHYP0IkiHyRvaB.fNCEVGKTM2ZgjeuF/Jd1IVfwFDft0pS</t>
   </si>
   <si>
     <t>01-01-2000</t>
@@ -58,13 +58,25 @@
     <t>Mihai14</t>
   </si>
   <si>
-    <t>mihai@gmail.com</t>
-  </si>
-  <si>
-    <t>$2a$12$AomzYMZwq2MjzsPAN9kK3OM6OheRkKWP/FSsBfbCDMiWqxvixmn1.</t>
-  </si>
-  <si>
-    <t>11-09-1100</t>
+    <t>mihaiviorelstan@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$dFXj26exmWO1qy1T8a2BJO1WUG5Bx808hZ.bWQBValcptUoiJYIYu</t>
+  </si>
+  <si>
+    <t>15-05-2004</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Mihai12</t>
+  </si>
+  <si>
+    <t>mihaiviis@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$8Ybnu3VPciLD5s9d507TLejcyGmjm94j2uh5LRMKZ7NfvtgHH1ca2</t>
   </si>
 </sst>
 </file>
@@ -437,13 +449,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.23046875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="65.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="63.4765625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
@@ -498,6 +510,23 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -65,6 +65,57 @@
   </si>
   <si>
     <t>11-09-1100</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>$2a$12$HDQ4cNX2tqwm7mOtB/Ngie0v6R.DBxORQaZUAaapcwKcRf.mgv.bO</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>$2a$12$jZo6Yy0QVVb1PmLBZ1WNZ.sQPMK2Plz.ZbqjN7121wxRQt1vpK4MC</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>$2a$12$B9pDOoHyeMxnEv/8W93qAeNZWrW2BehCcLjq.DX8CrlBIMLxg0qFu</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Serban123</t>
+  </si>
+  <si>
+    <t>2@y.com</t>
+  </si>
+  <si>
+    <t>$2a$12$LEmc/Jt7ZGNXFGtUdp/LI.ND/BIftqlcX00nGu4qkkTWRSRXedNwO</t>
+  </si>
+  <si>
+    <t>30-08-2000</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>$2a$12$xBjaZf1EvExCIPvl2PZo6.DbGfTkj7VLdmQGfPKt.uGb0Qv97F5T6</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>$2a$12$CWleeXeQLt2DgQ4ielPv..X4G/lPNgL9Eqo9BOHkuRe./qYGHIDFC</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>$2a$12$pTI6Arhn2a9Q53zdiblfAu2BYr68N5t07I653hOr.O/Fkw/sq8mFi</t>
   </si>
 </sst>
 </file>
@@ -437,11 +488,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="15.23046875"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="65.36328125"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
@@ -498,6 +549,125 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -77,6 +77,36 @@
   </si>
   <si>
     <t>$2a$12$8Ybnu3VPciLD5s9d507TLejcyGmjm94j2uh5LRMKZ7NfvtgHH1ca2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Serban123</t>
+  </si>
+  <si>
+    <t>s@y.com</t>
+  </si>
+  <si>
+    <t>$2a$12$e.OoKtEB9ipvvbtnSkRpTu.CWK64XxuPRjy7Yxa/CoZBLfeAt1zai</t>
+  </si>
+  <si>
+    <t>30-08-2000</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Serban12</t>
+  </si>
+  <si>
+    <t>s@ya.com</t>
+  </si>
+  <si>
+    <t>$2a$12$9p3ngfxICKBp6WSmh3Wjt.DzchQDtV6lcUdbW3CVrXoN1QQxTBfMm</t>
+  </si>
+  <si>
+    <t>30-05-2000</t>
   </si>
 </sst>
 </file>
@@ -449,13 +479,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="63.4765625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="63.87109375"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
@@ -527,6 +557,40 @@
         <v>14</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3AA2ED-248E-4D19-BB1F-F5DC9E904FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78A6D85-294C-4E67-8CC7-35DBC12456AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -46,7 +46,7 @@
     <t>test@admin</t>
   </si>
   <si>
-    <t>$2a$12$.8f5of5jHYP0IkiHyRvaB.fNCEVGKTM2ZgjeuF/Jd1IVfwFDft0pS</t>
+    <t>$2a$12$gjHVm51ixJlapO/reUNmO.v3l8SSAQ7Y4vADbl0i.ji/PSMsRVAEG</t>
   </si>
   <si>
     <t>01-01-2000</t>
@@ -61,52 +61,10 @@
     <t>mihaiviorelstan@gmail.com</t>
   </si>
   <si>
-    <t>$2a$12$dFXj26exmWO1qy1T8a2BJO1WUG5Bx808hZ.bWQBValcptUoiJYIYu</t>
+    <t>$2a$12$x21oBRHzFm8wgynDXaVhKu43EiOGSSlAPLMMbPbtD67rLG9GjL98S</t>
   </si>
   <si>
     <t>15-05-2004</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Mihai12</t>
-  </si>
-  <si>
-    <t>mihaiviis@gmail.com</t>
-  </si>
-  <si>
-    <t>$2a$12$8Ybnu3VPciLD5s9d507TLejcyGmjm94j2uh5LRMKZ7NfvtgHH1ca2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Serban123</t>
-  </si>
-  <si>
-    <t>s@y.com</t>
-  </si>
-  <si>
-    <t>$2a$12$e.OoKtEB9ipvvbtnSkRpTu.CWK64XxuPRjy7Yxa/CoZBLfeAt1zai</t>
-  </si>
-  <si>
-    <t>30-08-2000</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Serban12</t>
-  </si>
-  <si>
-    <t>s@ya.com</t>
-  </si>
-  <si>
-    <t>$2a$12$9p3ngfxICKBp6WSmh3Wjt.DzchQDtV6lcUdbW3CVrXoN1QQxTBfMm</t>
-  </si>
-  <si>
-    <t>30-05-2000</t>
   </si>
 </sst>
 </file>
@@ -479,13 +437,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="63.87109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="64.77734375"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
@@ -540,57 +498,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -65,6 +65,21 @@
   </si>
   <si>
     <t>15-05-2004</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Serban123</t>
+  </si>
+  <si>
+    <t>s@y.com</t>
+  </si>
+  <si>
+    <t>$2a$12$tHB/BcWADwLz089oNX3zW.Yq3vmvJwOP8fI2SR3itI8IiB1R4/4Py</t>
+  </si>
+  <si>
+    <t>30-08-2000</t>
   </si>
 </sst>
 </file>
@@ -437,11 +452,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="64.77734375"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
@@ -498,6 +513,23 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serba\AppData\Roaming\SPB_Data\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78A6D85-294C-4E67-8CC7-35DBC12456AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF94661-B550-4FE7-B217-A040DA424623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -65,28 +65,12 @@
   </si>
   <si>
     <t>15-05-2004</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Serban123</t>
-  </si>
-  <si>
-    <t>s@y.com</t>
-  </si>
-  <si>
-    <t>$2a$12$tHB/BcWADwLz089oNX3zW.Yq3vmvJwOP8fI2SR3itI8IiB1R4/4Py</t>
-  </si>
-  <si>
-    <t>30-08-2000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -452,82 +436,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="64.77734375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="E3" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -65,6 +65,21 @@
   </si>
   <si>
     <t>30-08-2000</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>mmmmm213</t>
+  </si>
+  <si>
+    <t>s@yy.com</t>
+  </si>
+  <si>
+    <t>$2a$12$jmwxQzadIykWO2nuswoyVeS7mk3.DAg066p3RKSY69qAL9BVVRcqq</t>
+  </si>
+  <si>
+    <t>30-09-2000</t>
   </si>
 </sst>
 </file>
@@ -437,13 +452,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.40234375"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="10.53515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="63.77734375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="64.48046875"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
@@ -481,23 +496,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -80,6 +80,18 @@
   </si>
   <si>
     <t>30-09-2000</t>
+  </si>
+  <si>
+    <t>Mihai14</t>
+  </si>
+  <si>
+    <t>mihai@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$qN.3gSO5DDZagJMmw98ayeZMdpkg8svoM4Ngu42ara.01oNbmDWsG</t>
+  </si>
+  <si>
+    <t>15-05-2004</t>
   </si>
 </sst>
 </file>
@@ -452,13 +464,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.40234375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="10.53515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="64.48046875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.23046875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="65.375"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
   <sheetData>
@@ -496,6 +508,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -92,6 +92,27 @@
   </si>
   <si>
     <t>15-05-2004</t>
+  </si>
+  <si>
+    <t>Mihai12</t>
+  </si>
+  <si>
+    <t>mihaiviorelstan@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$YzZWSJuSyxQx1rw11YlPruJqByi14NSE1.Lel34NnBFws0YmLsrey</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Mihai16</t>
+  </si>
+  <si>
+    <t>mihai16@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$jqncT20LIoitS7YBDlwA/ufkEftcLETLgvvUjN9BBpk4s.6T79k3O</t>
   </si>
 </sst>
 </file>
@@ -464,12 +485,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.23046875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="65.375"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
   </cols>
@@ -525,6 +546,40 @@
         <v>23</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serba\AppData\Roaming\SPB_Data\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ZTH-Team-Deltaspace\App\CLI-backend\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AC021C-E4B9-4D51-9972-4E1C4DB3646C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0960AB3A-7BB6-4714-89AB-2C712290C214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,33 +20,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>E-mail</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Date of Birth</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>Mihai14</t>
+  </si>
+  <si>
+    <t>mihai@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$KrX1r9FUsh4h/ZYtB9bT6.KfdzyeUDBuKfQ5Cl1mNhweqvkFrK7/a</t>
+  </si>
+  <si>
+    <t>15-05-2004</t>
+  </si>
+  <si>
     <t>admin</t>
   </si>
   <si>
     <t>test@admin</t>
   </si>
   <si>
-    <t>$2a$12$ujRTqg2rSOKzIxp7J1.2muCJwnb4bZOEQsMBm4p83xpYABg48nrRO</t>
+    <t>$2a$12$/6o6tGYyoQURmjO.Rrm20.NvcVIRUVh4VrPzUaQY18XkOplvHzqCi</t>
   </si>
   <si>
     <t>01-01-2000</t>
@@ -55,64 +52,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Serban123</t>
-  </si>
-  <si>
-    <t>s@y.com</t>
-  </si>
-  <si>
-    <t>$2a$12$32W30IdsvUHIp91q/MVbzu4ahL0jbmSZmss/d4UU53oS45C/L5RLy</t>
-  </si>
-  <si>
-    <t>30-08-2000</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>mmmmm213</t>
-  </si>
-  <si>
-    <t>s@yy.com</t>
-  </si>
-  <si>
-    <t>$2a$12$jmwxQzadIykWO2nuswoyVeS7mk3.DAg066p3RKSY69qAL9BVVRcqq</t>
-  </si>
-  <si>
-    <t>30-09-2000</t>
-  </si>
-  <si>
-    <t>Mihai14</t>
-  </si>
-  <si>
-    <t>mihai@gmail.com</t>
-  </si>
-  <si>
-    <t>$2a$12$qN.3gSO5DDZagJMmw98ayeZMdpkg8svoM4Ngu42ara.01oNbmDWsG</t>
-  </si>
-  <si>
-    <t>15-05-2004</t>
-  </si>
-  <si>
-    <t>Mihai12</t>
-  </si>
-  <si>
-    <t>mihaiviorelstan@gmail.com</t>
-  </si>
-  <si>
-    <t>$2a$12$YzZWSJuSyxQx1rw11YlPruJqByi14NSE1.Lel34NnBFws0YmLsrey</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Mihai16</t>
-  </si>
-  <si>
-    <t>mihai16@gmail.com</t>
-  </si>
-  <si>
-    <t>$2a$12$jqncT20LIoitS7YBDlwA/ufkEftcLETLgvvUjN9BBpk4s.6T79k3O</t>
+    <t>$2a$12$Nba9LbbhluPg7MAKtSvXD.9nlG.iY.WecDEQ2baUr0.2i1wG5.bvW</t>
   </si>
 </sst>
 </file>
@@ -485,17 +425,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="2.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.20703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="22.92578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="65.375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.91015625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="1.9140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="7.2109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.23046875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="62.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.11328125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
@@ -512,72 +452,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="D2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="E2" t="s" s="0">
         <v>8</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>22</v>
-      </c>
       <c r="E3" t="s" s="0">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/App/CLI-backend/databases/UserDatabase.xlsx
+++ b/App/CLI-backend/databases/UserDatabase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>1</t>
   </si>
@@ -53,6 +53,18 @@
   </si>
   <si>
     <t>$2a$12$Nba9LbbhluPg7MAKtSvXD.9nlG.iY.WecDEQ2baUr0.2i1wG5.bvW</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Mihai12</t>
+  </si>
+  <si>
+    <t>mihaistan@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$12$qaqRQWR./udlP/6RlKRh.eATubFWV8mSD75/fF8sSEUL5wLOynFl2</t>
   </si>
 </sst>
 </file>
@@ -425,13 +437,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="1.9140625"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="7.2109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.23046875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="62.171875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="18.62890625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="62.4765625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="10.11328125"/>
   </cols>
   <sheetData>
@@ -486,6 +498,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
